--- a/InputData/bldgs/EoCEDwEC/Elast of Component E Demand wrt E Cost.xlsx
+++ b/InputData/bldgs/EoCEDwEC/Elast of Component E Demand wrt E Cost.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rachel Goldstein\Dropbox (Energy Innovation)\Desktop\Vensim files from GitHub\EPS US\InputData\bldgs\EoCEDwEC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RobbieOrvis\Models\EPS Structure Research\eps-us-dc-replay\InputData\bldgs\EoCEDwEC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D67715FF-ECB8-403C-85D4-482D3A4407C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E67D39B-DAB0-4F9B-A527-BCAA38CCA857}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29580" yWindow="825" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="23520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -27,6 +27,7 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="57">
   <si>
     <t>EoCEDwEC Elasticity of Component Energy Demand wrt Energy Cost</t>
   </si>
@@ -196,6 +197,15 @@
   </si>
   <si>
     <t xml:space="preserve">**Note from April 2023 - there has not been an updated version of this report. This is the most recent own-price elasticity data </t>
+  </si>
+  <si>
+    <t>Data Centers</t>
+  </si>
+  <si>
+    <t>Data centers</t>
+  </si>
+  <si>
+    <t>Data centers are a separate building type. They use the commercial values, so the data-centers column copies the commercial column.</t>
   </si>
 </sst>
 </file>
@@ -383,7 +393,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -419,6 +429,9 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -488,9 +501,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -528,9 +541,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -563,26 +576,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -615,26 +611,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -808,7 +787,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="67.42578125" customWidth="1"/>
@@ -950,6 +929,14 @@
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>44</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B33" s="24" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -1233,7 +1220,7 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.140625" customWidth="1"/>
@@ -1241,7 +1228,7 @@
     <col min="4" max="4" width="15.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>45</v>
       </c>
@@ -1254,8 +1241,11 @@
       <c r="D1" s="20" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -1271,8 +1261,12 @@
         <f>'EIA Table 1'!E14-'EIA Table 1'!D14</f>
         <v>-0.03</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E2">
+        <f>$D2</f>
+        <v>-0.03</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -1288,8 +1282,12 @@
         <f>D5</f>
         <v>-3.999999999999998E-2</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E3">
+        <f>$D3</f>
+        <v>-3.999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -1305,8 +1303,12 @@
         <f>'EIA Table 1'!F15-'EIA Table 1'!D15</f>
         <v>-3.0000000000000027E-2</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E4">
+        <f>$D4</f>
+        <v>-3.0000000000000027E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -1322,8 +1324,12 @@
         <f>'EIA Table 1'!G16-'EIA Table 1'!D16</f>
         <v>-3.999999999999998E-2</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E5">
+        <f>$D5</f>
+        <v>-3.999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -1337,8 +1343,12 @@
       <c r="D6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E6">
+        <f>$D6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>34</v>
       </c>
@@ -1351,8 +1361,12 @@
       <c r="D7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E7">
+        <f>$D7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>37</v>
       </c>
@@ -1368,8 +1382,12 @@
         <f t="shared" si="1"/>
         <v>-3.999999999999998E-2</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E8">
+        <f>$D8</f>
+        <v>-3.999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>38</v>
       </c>
@@ -1385,8 +1403,12 @@
         <f t="shared" si="2"/>
         <v>-3.999999999999998E-2</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E9">
+        <f>$D9</f>
+        <v>-3.999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>39</v>
       </c>
@@ -1402,8 +1424,12 @@
         <f t="shared" si="3"/>
         <v>-3.0000000000000027E-2</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E10">
+        <f>$D10</f>
+        <v>-3.0000000000000027E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>40</v>
       </c>
@@ -1417,6 +1443,10 @@
       </c>
       <c r="D11" s="21">
         <f t="shared" si="4"/>
+        <v>-0.03</v>
+      </c>
+      <c r="E11">
+        <f>$D11</f>
         <v>-0.03</v>
       </c>
     </row>
